--- a/data/trans_orig/P19C10_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,74 +730,74 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1844</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3671</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>712</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3329</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303586</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284278</t>
+          <t>283936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287448</t>
+          <t>287607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>588891</t>
+          <t>590241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6892</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499911</t>
+          <t>500092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497513</t>
+          <t>497437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1000235</t>
+          <t>1000835</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1007988</t>
+          <t>1007981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>299521</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326040</t>
+          <t>326233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334031</t>
+          <t>334006</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627091</t>
+          <t>627182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635220</t>
+          <t>635204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>308060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>468408</t>
+          <t>468917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473115</t>
+          <t>473161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>779182</t>
+          <t>777494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783258</t>
+          <t>783226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,62 +2137,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165568</t>
+          <t>165795</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>201479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368296</t>
+          <t>368507</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,97 +2445,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1412</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>339</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1902</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252320</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244448</t>
+          <t>244755</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498186</t>
+          <t>498366</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23099</t>
+          <t>22920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>585000</t>
+          <t>584838</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597120</t>
+          <t>597078</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>815188</t>
+          <t>815578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>825942</t>
+          <t>825879</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1404961</t>
+          <t>1405140</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1420812</t>
+          <t>1420911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>899240</t>
+          <t>900749</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>693560</t>
+          <t>693516</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>701722</t>
+          <t>701689</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1597321</t>
+          <t>1598864</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1609792</t>
+          <t>1609914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29381</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3335268</t>
+          <t>3334420</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3350039</t>
+          <t>3349189</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3549446</t>
+          <t>3549938</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3565630</t>
+          <t>3565329</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6890059</t>
+          <t>6891140</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6912061</t>
+          <t>6911703</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C10_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>995</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>286895</t>
+          <t>308469</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283936</t>
+          <t>306441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>592325</t>
+          <t>609386</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>590241</t>
+          <t>606866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,42 +1128,42 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2546</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>8608</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7697</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505572</t>
+          <t>516672</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500092</t>
+          <t>511906</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,67 +1216,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>500401</t>
+          <t>530422</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497437</t>
+          <t>527906</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1047094</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1041032</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1049053</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>99,18%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1005972</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1000835</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1007981</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>331500</t>
+          <t>337930</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326233</t>
+          <t>332704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334006</t>
+          <t>340416</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>632692</t>
+          <t>638160</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627182</t>
+          <t>632116</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635204</t>
+          <t>640688</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>301192</t>
+          <t>300231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>636467</t>
+          <t>641935</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>471818</t>
+          <t>417878</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>468917</t>
+          <t>414670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>473161</t>
+          <t>419282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>781938</t>
+          <t>788616</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>777494</t>
+          <t>785141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>783226</t>
+          <t>790012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,96%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>500</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2210,27 +2210,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>167952</t>
+          <t>188799</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165795</t>
+          <t>186860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>370244</t>
+          <t>408601</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368507</t>
+          <t>406600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>349</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>246011</t>
+          <t>251211</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244755</t>
+          <t>249654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,17 +2623,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>499743</t>
+          <t>500945</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>498366</t>
+          <t>498963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,102 +2783,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4617</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>14990</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>16164</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>9365</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>24660</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>7068</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>12787</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>13813</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>7149</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>22920</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -2896,102 +2896,102 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>592950</t>
+          <t>690623</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584838</t>
+          <t>683084</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>597078</t>
+          <t>695253</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>732279</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>726396</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>736769</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,77%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1486</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1422902</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1414406</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1429701</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>98,88%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>821297</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>815578</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>825879</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,46%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1486</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1414247</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1405140</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1420911</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>599695</t>
+          <t>697680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1428060</t>
+          <t>1439066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13699</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -3239,27 +3239,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>906996</t>
+          <t>769208</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>900749</t>
+          <t>761248</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>698751</t>
+          <t>804475</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>693516</t>
+          <t>798466</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>701689</t>
+          <t>807810</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1605747</t>
+          <t>1573683</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1598864</t>
+          <t>1566178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1609914</t>
+          <t>1578130</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,22 +3469,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41908</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -3582,27 +3582,27 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3343944</t>
+          <t>3386923</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3334420</t>
+          <t>3377137</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3349189</t>
+          <t>3392659</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3558965</t>
+          <t>3602464</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3549938</t>
+          <t>3592411</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3565329</t>
+          <t>3609717</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6902909</t>
+          <t>6989386</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6891140</t>
+          <t>6976499</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6911703</t>
+          <t>6998740</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
